--- a/test-import-valid.xlsx
+++ b/test-import-valid.xlsx
@@ -150,13 +150,13 @@
     <t>S</t>
   </si>
   <si>
-    <t>下界尺寸組合</t>
+    <t>下界尺寸組合 (W70/L70)</t>
   </si>
   <si>
     <t>3XL</t>
   </si>
   <si>
-    <t>上界尺寸組合</t>
+    <t>上界尺寸組合 (W110/L90)</t>
   </si>
   <si>
     <t>RT018378</t>
@@ -820,10 +820,10 @@
         <v>42</v>
       </c>
       <c r="F2" s="2">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -852,10 +852,10 @@
         <v>42</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -884,10 +884,10 @@
         <v>42</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="G4">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -948,10 +948,10 @@
         <v>50</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -980,10 +980,10 @@
         <v>55</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H7">
         <v>2</v>
